--- a/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
+++ b/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N180"/>
+  <dimension ref="A1:N179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,75 +1444,67 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,21 +1514,13 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1536,23 +1528,31 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1586,21 +1586,29 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1610,7 +1618,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1644,24 +1652,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1671,8 +1679,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1680,63 +1696,47 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,21 +1754,29 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1812,19 +1820,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1868,19 +1876,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1924,19 +1932,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1980,19 +1988,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2026,29 +2034,21 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,64 +2111,56 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2176,23 +2168,31 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,21 +2226,29 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2284,24 +2292,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2311,72 +2319,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,21 +2394,29 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2452,19 +2460,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2482,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2516,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2564,19 +2572,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2628,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2642,77 +2650,61 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
@@ -2720,28 +2712,36 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-applies</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>Biodiversity gain condition exemption reason[]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>exemption-type</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Exemption type</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>exemption-type</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2784,12 +2784,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2808,22 +2808,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2832,12 +2832,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2880,12 +2880,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2928,17 +2928,17 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Habitat loss after 2020</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2976,12 +2976,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3010,31 +3010,39 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>loss-date</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Loss date</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3068,24 +3076,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>loss-date</t>
+          <t>pre-loss-biodiversity-value</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Loss date</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3124,29 +3132,29 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>pre-loss-biodiversity-value</t>
+          <t>supporting-evidence</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Supporting evidence</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3170,39 +3178,31 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>supporting-evidence</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Supporting evidence</t>
-        </is>
-      </c>
+          <t>Metric publication date</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3240,12 +3240,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>irreplaceable-habitats-details</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Irreplaceable habitats details</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3288,17 +3288,17 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3322,21 +3322,29 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3346,53 +3354,45 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>supporting-documents</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3409,27 +3409,27 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>conflict-of-interest</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3440,12 +3440,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3455,16 +3455,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3472,12 +3464,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3488,17 +3480,17 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3504,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3528,7 +3520,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3543,21 +3535,29 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3568,7 +3568,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3578,21 +3578,13 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3600,12 +3592,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3616,12 +3608,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3640,12 +3632,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3656,12 +3648,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3671,37 +3663,53 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>full-time</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3711,16 +3719,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>employment</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3800,7 +3800,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -3824,22 +3824,22 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3944,7 +3944,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3959,31 +3959,39 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>existing-use</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing use details[]</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3992,12 +4000,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -4007,16 +4015,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>existing-use</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>use-details</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -4048,17 +4048,17 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4082,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>use-details</t>
+          <t>land-part</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Land part</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -4096,7 +4096,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4120,36 +4120,28 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>land-part</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Land part</t>
-        </is>
-      </c>
+          <t>Site vacant</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4168,12 +4160,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4184,17 +4176,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4200,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4224,12 +4216,12 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4248,12 +4240,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4264,17 +4256,17 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4280,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4304,7 +4296,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4328,12 +4320,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4344,7 +4336,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4368,12 +4360,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4384,36 +4376,44 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4424,31 +4424,23 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Results of any flood risk assessments made for the development site</t>
@@ -4456,12 +4448,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-area</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4472,17 +4464,17 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4488,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>data-provided-by</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4512,12 +4504,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4536,12 +4528,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4552,17 +4544,17 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4568,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4592,7 +4584,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4616,12 +4608,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4632,12 +4624,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4647,32 +4639,48 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="2" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -4687,16 +4695,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>hrs-operation</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -4728,17 +4728,17 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4762,31 +4762,39 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>operational-times</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>day-type</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Day type</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Day or type of day</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4820,29 +4828,29 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>day-type</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4876,29 +4884,37 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>time-ranges</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>open-time</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4942,17 +4958,17 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>open-time</t>
+          <t>close-time</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Open time</t>
+          <t>Close time</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -4986,109 +5002,85 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>hours-not-known</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>time-ranges</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>close-time</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Hours not known</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>non-res-floorspace</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>non-residential-change-outline</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>hours-not-known</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>non-res-floorspace</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Details of changes to non-residential floorspace in the proposed development.</t>
@@ -5096,23 +5088,31 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>non-residential-change-outline</t>
+          <t>floorspace-details-outline</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+          <t>Floorspace details[]</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>specified-use</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5160,17 +5160,17 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>specified-use</t>
+          <t>not-applicable</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5208,12 +5208,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Whether the facility is not applicable</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>not-applicable</t>
+          <t>existing-gross-floorspace</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5256,17 +5256,17 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5290,12 +5290,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>existing-gross-floorspace</t>
+          <t>is-floorspace-lost-known</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Is floorspace lost known</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5304,17 +5304,17 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>Whether the amount of floorspace to be lost is known</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>is-floorspace-lost-known</t>
+          <t>floorspace-lost</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Is floorspace lost known</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -5352,12 +5352,12 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Whether the amount of floorspace to be lost is known</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>floorspace-lost</t>
+          <t>is-total-gross-proposed-known</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Is total gross proposed known</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5400,12 +5400,12 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>Whether the total gross proposed floorspace is known</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>is-total-gross-proposed-known</t>
+          <t>total-gross-proposed</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Is total gross proposed known</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5448,12 +5448,12 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Whether the total gross proposed floorspace is known</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>total-gross-proposed</t>
+          <t>net-additional-floorspace</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5496,7 +5496,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5520,22 +5520,22 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>floorspace-details-outline</t>
+          <t>room-details-outline</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Room details[]</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>net-additional-floorspace</t>
+          <t>use-class-accommodation</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5544,12 +5544,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>use-class-accommodation</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5592,17 +5592,17 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5626,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>not-applicable</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5640,12 +5640,12 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Used to explicitly state the use class does not apply to the proposal</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>not-applicable</t>
+          <t>is-existing-rooms-lost-known</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Is existing rooms lost known</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -5688,7 +5688,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Used to explicitly state the use class does not apply to the proposal</t>
+          <t>Whether the total existing rooms that will be lost is known</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>is-existing-rooms-lost-known</t>
+          <t>existing-rooms-lost</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Is existing rooms lost known</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5736,12 +5736,12 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Whether the total existing rooms that will be lost is known</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>existing-rooms-lost</t>
+          <t>is-total-rooms-proposed-known</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Is total rooms proposed known</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5784,12 +5784,12 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Whether the total rooms proposed is known</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>is-total-rooms-proposed-known</t>
+          <t>total-rooms-proposed</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Is total rooms proposed known</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -5832,12 +5832,12 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Whether the total rooms proposed is known</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>total-rooms-proposed</t>
+          <t>net-additional-rooms</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Net additional rooms</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -5880,7 +5880,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -5890,50 +5890,50 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="2" t="n"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>room-details-outline</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>net-additional-rooms</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Net additional rooms</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -5943,16 +5943,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -5960,12 +5952,12 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -5976,7 +5968,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -6000,33 +5992,49 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6060,19 +6068,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -6082,7 +6090,7 @@
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6116,19 +6124,19 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -6172,19 +6180,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -6228,19 +6236,19 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -6250,7 +6258,7 @@
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6274,34 +6282,26 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-date</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -6320,36 +6320,28 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>notice-date</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -6368,23 +6360,31 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>publication-date</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -6432,12 +6432,12 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -6456,41 +6456,33 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6504,12 +6496,12 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>applicant-signature</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
@@ -6520,12 +6512,12 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -6544,12 +6536,12 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>agent-signature</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
@@ -6560,7 +6552,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -6584,12 +6576,12 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
@@ -6600,7 +6592,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -6615,21 +6607,29 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n"/>
-      <c r="B124" s="2" t="n"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -6640,31 +6640,23 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -6672,12 +6664,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -6688,17 +6680,17 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6712,12 +6704,12 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
@@ -6728,7 +6720,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -6752,12 +6744,12 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -6768,7 +6760,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -6792,12 +6784,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -6808,7 +6800,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -6823,21 +6815,29 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n"/>
-      <c r="B129" s="2" t="n"/>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>processes-machinery-waste</t>
+        </is>
+      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>How waste will be managed on the site</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>site-activity-details</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
@@ -6848,7 +6848,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -6858,21 +6858,13 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>processes-machinery-waste</t>
-        </is>
-      </c>
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>How waste will be managed on the site</t>
@@ -6880,12 +6872,12 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>site-activity-details</t>
+          <t>proposal-waste-management</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Proposal waste management</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
@@ -6896,12 +6888,12 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Whether the proposal involves waste management development</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -6920,28 +6912,36 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>proposal-waste-management</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>waste-management-facility-type</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Waste management facility type</t>
+        </is>
+      </c>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Type of waste management facility</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>waste-management-facility-type</t>
+          <t>not-applicable</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Waste management facility type</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
@@ -6984,17 +6984,17 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Whether the facility is not applicable</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>not-applicable</t>
+          <t>total-capacity</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
@@ -7032,12 +7032,12 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>total-capacity</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -7080,12 +7080,12 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>annual-throughput</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
@@ -7128,12 +7128,12 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>annual-throughput</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -7176,12 +7176,12 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -7200,22 +7200,22 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>municipal</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7224,12 +7224,12 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>municipal</t>
+          <t>construction-demolition</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
@@ -7272,7 +7272,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>construction-demolition</t>
+          <t>commercial-industrial</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr"/>
@@ -7320,7 +7320,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>commercial-industrial</t>
+          <t>hazardous</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr"/>
@@ -7368,7 +7368,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -7383,64 +7383,56 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n"/>
-      <c r="B141" s="2" t="n"/>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>proposal-description</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>hazardous</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -7448,12 +7440,12 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>reserved-matters</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reserved matters[]</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -7464,12 +7456,12 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -7488,12 +7480,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>reserved-matters</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7504,12 +7496,12 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -7528,12 +7520,12 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7544,17 +7536,17 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7560,12 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -7584,17 +7576,17 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7608,12 +7600,12 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -7624,36 +7616,44 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="2" t="n"/>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>res-units</t>
+        </is>
+      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>will-residential-units-change</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -7664,31 +7664,23 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>res-units</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Details of the residential units that make up both the current and proposed development.</t>
@@ -7696,28 +7688,36 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>will-residential-units-change</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>tenure-type</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>tenure-type</t>
+          <t>housing-type</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr"/>
@@ -7760,7 +7760,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -7794,26 +7794,34 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>housing-type</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>units-unknown</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -7852,19 +7860,27 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="inlineStr"/>
-      <c r="K151" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
@@ -7918,27 +7934,27 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7982,17 +7998,17 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
@@ -8002,7 +8018,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8036,27 +8052,19 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -8066,7 +8074,7 @@
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8090,39 +8098,39 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>proposed-unit-breakdown</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr"/>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8156,19 +8164,27 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="inlineStr"/>
-      <c r="K156" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -8222,27 +8238,27 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8286,17 +8302,17 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -8306,7 +8322,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8340,27 +8356,19 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
@@ -8370,7 +8378,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8384,39 +8392,23 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>total-existing-units</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>proposed-unit-breakdown</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>total-units</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -8426,7 +8418,7 @@
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8440,12 +8432,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>total-existing-units</t>
+          <t>total-proposed-units</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8456,7 +8448,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
@@ -8480,12 +8472,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>total-proposed-units</t>
+          <t>net-change</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8496,7 +8488,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
@@ -8511,21 +8503,29 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n"/>
-      <c r="B163" s="2" t="n"/>
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>site-area</t>
+        </is>
+      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>net-change</t>
+          <t>site-area-in-hectares</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8536,7 +8536,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -8551,16 +8551,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>site-area</t>
-        </is>
-      </c>
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>How big the site is including relevant measurements</t>
@@ -8568,12 +8560,12 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>site-area-in-hectares</t>
+          <t>site-area-provided-by</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
@@ -8584,52 +8576,68 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n"/>
-      <c r="B165" s="2" t="n"/>
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>site-area-provided-by</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H165" s="2" t="inlineStr"/>
       <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="2" t="inlineStr"/>
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -8639,16 +8647,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -8666,12 +8666,12 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
@@ -8680,12 +8680,12 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
@@ -8728,7 +8728,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr"/>
@@ -8776,12 +8776,12 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr"/>
@@ -8824,7 +8824,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr"/>
@@ -8872,7 +8872,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -8920,7 +8920,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr"/>
@@ -8968,12 +8968,12 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
@@ -9016,7 +9016,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
@@ -9031,64 +9031,56 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n"/>
-      <c r="B174" s="2" t="n"/>
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr"/>
       <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
       <c r="C175" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -9096,12 +9088,12 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr"/>
@@ -9112,12 +9104,12 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
@@ -9136,12 +9128,12 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr"/>
@@ -9152,17 +9144,17 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9176,23 +9168,31 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr"/>
-      <c r="G177" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="2" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9226,12 +9226,12 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
@@ -9240,7 +9240,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -9288,7 +9288,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -9297,54 +9297,6 @@
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="n"/>
-      <c r="B180" s="2" t="n"/>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>other-contact</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr"/>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M180" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -9352,50 +9304,50 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A110:A124"/>
-    <mergeCell ref="A42:A55"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A130:A141"/>
-    <mergeCell ref="A125:A129"/>
-    <mergeCell ref="A79:A84"/>
-    <mergeCell ref="B166:B174"/>
-    <mergeCell ref="B92:B109"/>
-    <mergeCell ref="A85:A91"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A69:A78"/>
-    <mergeCell ref="B130:B141"/>
-    <mergeCell ref="B63:B68"/>
-    <mergeCell ref="B125:B129"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B175:B180"/>
-    <mergeCell ref="B56"/>
-    <mergeCell ref="A148:A163"/>
-    <mergeCell ref="A92:A109"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B85:B91"/>
-    <mergeCell ref="A142:A147"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A175:A180"/>
-    <mergeCell ref="B69:B78"/>
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="B110:B124"/>
-    <mergeCell ref="A166:A174"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B148:B163"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="A63:A68"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="A68:A77"/>
+    <mergeCell ref="B141:B146"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B147:B162"/>
+    <mergeCell ref="B109:B123"/>
+    <mergeCell ref="B55"/>
+    <mergeCell ref="B129:B140"/>
+    <mergeCell ref="A147:A162"/>
+    <mergeCell ref="B124:B128"/>
+    <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="A78:A83"/>
+    <mergeCell ref="A91:A108"/>
+    <mergeCell ref="A174:A179"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B41:B54"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="A165:A173"/>
+    <mergeCell ref="B91:B108"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B174:B179"/>
+    <mergeCell ref="A109:A123"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A141:A146"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A124:A128"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="A84:A90"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="A41:A54"/>
+    <mergeCell ref="B165:B173"/>
+    <mergeCell ref="B68:B77"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="A129:A140"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
+++ b/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
@@ -4772,19 +4772,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>day-type</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
+++ b/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
@@ -3653,7 +3653,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
+++ b/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N179"/>
+  <dimension ref="A1:N178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -6827,7 +6827,8 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -6867,7 +6868,8 @@
       <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -6888,7 +6890,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -6907,7 +6909,8 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -6936,7 +6939,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -6955,7 +6958,8 @@
       <c r="B132" s="2" t="n"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -6970,12 +6974,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>not-applicable</t>
+          <t>total-capacity</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
@@ -6984,17 +6988,17 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7007,8 @@
       <c r="B133" s="2" t="n"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -7018,12 +7023,12 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>total-capacity</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
@@ -7032,17 +7037,17 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7056,8 @@
       <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -7066,12 +7072,12 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>annual-throughput</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -7080,17 +7086,17 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7105,8 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -7114,12 +7121,12 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>annual-throughput</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
@@ -7128,17 +7135,17 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7147,27 +7154,28 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>municipal</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -7176,12 +7184,12 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -7195,7 +7203,8 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -7210,12 +7219,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>municipal</t>
+          <t>construction-demolition</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7224,7 +7233,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -7243,7 +7252,8 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -7258,12 +7268,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>construction-demolition</t>
+          <t>commercial-industrial</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
@@ -7272,7 +7282,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -7291,7 +7301,8 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -7306,12 +7317,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>commercial-industrial</t>
+          <t>hazardous</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr"/>
@@ -7320,7 +7331,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -7335,64 +7346,56 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n"/>
-      <c r="B140" s="2" t="n"/>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>hazardous</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -7400,12 +7403,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reserved-matters</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reserved matters[]</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -7416,12 +7419,12 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -7440,12 +7443,12 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>reserved-matters</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -7456,12 +7459,12 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -7480,12 +7483,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7496,17 +7499,17 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7520,12 +7523,12 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7536,17 +7539,17 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7560,12 +7563,12 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -7576,36 +7579,44 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="2" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>res-units</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>will-residential-units-change</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -7616,31 +7627,23 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>res-units</t>
-        </is>
-      </c>
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Details of the residential units that make up both the current and proposed development.</t>
@@ -7648,28 +7651,36 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>will-residential-units-change</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>tenure-type</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -7698,12 +7709,12 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>tenure-type</t>
+          <t>housing-type</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
@@ -7712,7 +7723,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -7746,26 +7757,34 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>housing-type</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr"/>
-      <c r="I149" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>units-unknown</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -7804,19 +7823,27 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr"/>
-      <c r="K150" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -7870,27 +7897,27 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7934,17 +7961,17 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -7954,7 +7981,7 @@
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7988,27 +8015,19 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
@@ -8018,7 +8037,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8042,39 +8061,39 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>proposed-unit-breakdown</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8108,19 +8127,27 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="inlineStr"/>
-      <c r="K155" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
@@ -8174,27 +8201,27 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8238,17 +8265,17 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
@@ -8258,7 +8285,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8292,27 +8319,19 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -8322,7 +8341,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8336,39 +8355,23 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>total-existing-units</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>proposed-unit-breakdown</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>total-units</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
@@ -8378,7 +8381,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8392,12 +8395,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>total-existing-units</t>
+          <t>total-proposed-units</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -8408,7 +8411,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -8432,12 +8435,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>total-proposed-units</t>
+          <t>net-change</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8448,7 +8451,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
@@ -8463,21 +8466,29 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="n"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>site-area</t>
+        </is>
+      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>net-change</t>
+          <t>site-area-in-hectares</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8488,7 +8499,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
@@ -8503,16 +8514,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>site-area</t>
-        </is>
-      </c>
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>How big the site is including relevant measurements</t>
@@ -8520,12 +8523,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>site-area-in-hectares</t>
+          <t>site-area-provided-by</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8536,52 +8539,68 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="2" t="n"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>site-area-provided-by</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H164" s="2" t="inlineStr"/>
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -8591,16 +8610,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -8618,12 +8629,12 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr"/>
@@ -8632,12 +8643,12 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -8666,12 +8677,12 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
@@ -8680,7 +8691,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
@@ -8714,12 +8725,12 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
@@ -8728,12 +8739,12 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -8762,12 +8773,12 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr"/>
@@ -8776,7 +8787,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
@@ -8810,12 +8821,12 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr"/>
@@ -8824,7 +8835,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
@@ -8858,12 +8869,12 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr"/>
@@ -8872,7 +8883,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
@@ -8906,12 +8917,12 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -8920,12 +8931,12 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -8954,12 +8965,12 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr"/>
@@ -8968,7 +8979,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
@@ -8983,64 +8994,56 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n"/>
-      <c r="B173" s="2" t="n"/>
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr"/>
       <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="2" t="inlineStr"/>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
       <c r="C174" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -9048,12 +9051,12 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr"/>
@@ -9064,12 +9067,12 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -9088,12 +9091,12 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr"/>
@@ -9104,17 +9107,17 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9128,23 +9131,31 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr"/>
-      <c r="G176" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H176" s="2" t="inlineStr"/>
       <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
@@ -9154,7 +9165,7 @@
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9189,12 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -9192,7 +9203,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -9226,12 +9237,12 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
@@ -9240,7 +9251,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -9249,54 +9260,6 @@
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="n"/>
-      <c r="B179" s="2" t="n"/>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>other-contact</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr"/>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M179" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N179" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -9306,46 +9269,46 @@
   <mergeCells count="44">
     <mergeCell ref="B35:B40"/>
     <mergeCell ref="A68:A77"/>
-    <mergeCell ref="B141:B146"/>
     <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B147:B162"/>
+    <mergeCell ref="B146:B161"/>
     <mergeCell ref="B109:B123"/>
     <mergeCell ref="B55"/>
-    <mergeCell ref="B129:B140"/>
-    <mergeCell ref="A147:A162"/>
+    <mergeCell ref="A164:A172"/>
     <mergeCell ref="B124:B128"/>
     <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B140:B145"/>
+    <mergeCell ref="A162:A163"/>
     <mergeCell ref="B2:B18"/>
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="B62:B67"/>
     <mergeCell ref="A78:A83"/>
     <mergeCell ref="A91:A108"/>
-    <mergeCell ref="A174:A179"/>
+    <mergeCell ref="A129:A139"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B41:B54"/>
     <mergeCell ref="B19:B22"/>
     <mergeCell ref="B59:B61"/>
+    <mergeCell ref="B162:B163"/>
     <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="A173:A178"/>
+    <mergeCell ref="B164:B172"/>
     <mergeCell ref="B78:B83"/>
-    <mergeCell ref="A165:A173"/>
     <mergeCell ref="B91:B108"/>
     <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B174:B179"/>
+    <mergeCell ref="B129:B139"/>
     <mergeCell ref="A109:A123"/>
     <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A141:A146"/>
+    <mergeCell ref="A146:A161"/>
     <mergeCell ref="A35:A40"/>
     <mergeCell ref="A124:A128"/>
-    <mergeCell ref="B163:B164"/>
     <mergeCell ref="A84:A90"/>
     <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A140:A145"/>
     <mergeCell ref="A55"/>
     <mergeCell ref="A41:A54"/>
-    <mergeCell ref="B165:B173"/>
     <mergeCell ref="B68:B77"/>
     <mergeCell ref="A23:A30"/>
-    <mergeCell ref="A129:A140"/>
+    <mergeCell ref="B173:B178"/>
     <mergeCell ref="A56:A58"/>
     <mergeCell ref="A62:A67"/>
   </mergeCells>

--- a/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
+++ b/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N178"/>
+  <dimension ref="A1:N177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,67 +1436,75 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,13 +1514,21 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1528,31 +1536,23 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1586,21 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1652,24 +1644,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1679,16 +1671,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1696,47 +1680,63 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,29 +1754,21 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1786,7 +1778,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1820,19 +1812,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1868,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1932,19 +1924,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1988,19 +1980,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2010,7 +2002,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2026,29 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,56 +2111,64 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2168,31 +2176,23 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,29 +2226,21 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2258,7 +2250,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2292,24 +2284,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2319,64 +2311,72 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,29 +2394,21 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2426,7 +2418,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2460,19 +2452,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2482,7 +2474,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2516,19 +2508,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2572,19 +2564,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2628,19 +2620,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2650,61 +2642,77 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-applies</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
@@ -2712,36 +2720,28 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>exemption-type</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>exemption-type</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2784,12 +2784,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2808,22 +2808,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2832,12 +2832,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2880,12 +2880,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2928,17 +2928,17 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2976,12 +2976,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3010,39 +3010,31 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>loss-date</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3076,24 +3068,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>pre-loss-biodiversity-value</t>
+          <t>loss-date</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3132,29 +3124,29 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>supporting-evidence</t>
+          <t>pre-loss-biodiversity-value</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3178,31 +3170,39 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>supporting-evidence</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3240,12 +3240,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3288,17 +3288,17 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3322,29 +3322,21 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>irreplaceable-habitats-details</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3354,45 +3346,53 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3409,27 +3409,27 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3440,12 +3440,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3455,8 +3455,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3464,12 +3472,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3480,17 +3488,17 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3504,12 +3512,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3520,7 +3528,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3535,29 +3543,21 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3568,7 +3568,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3578,13 +3578,21 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3592,12 +3600,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3608,12 +3616,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3632,12 +3640,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3648,12 +3656,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3663,53 +3671,37 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>employment</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>full-time</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3719,8 +3711,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3752,12 +3752,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3800,12 +3800,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3824,22 +3824,22 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3848,12 +3848,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3896,12 +3896,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3959,39 +3959,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>existing-use</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -4000,12 +3992,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -4015,8 +4007,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>existing-use</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>use-details</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -4048,17 +4048,17 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4082,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>land-part</t>
+          <t>use-details</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -4096,7 +4096,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4120,28 +4120,36 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>land-part</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4160,12 +4168,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4176,17 +4184,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4200,12 +4208,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4216,12 +4224,12 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4240,12 +4248,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4256,17 +4264,17 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4280,12 +4288,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4296,7 +4304,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4320,12 +4328,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4336,7 +4344,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4360,12 +4368,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4376,44 +4384,36 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-area</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4424,23 +4424,31 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="2" t="n"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Results of any flood risk assessments made for the development site</t>
@@ -4448,12 +4456,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>data-provided-by</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4464,17 +4472,17 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4496,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4504,12 +4512,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4528,12 +4536,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4544,17 +4552,17 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4568,12 +4576,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4584,7 +4592,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4608,12 +4616,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4624,12 +4632,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4639,48 +4647,32 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>hrs-operation</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Surface water disposal[]</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -4695,8 +4687,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="2" t="n"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -4728,17 +4728,17 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4762,39 +4762,31 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>schedule-days</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4828,29 +4820,29 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4884,37 +4876,29 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>open-time</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4958,17 +4942,17 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>close-time</t>
+          <t>open-time</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Close time</t>
+          <t>Open time</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -5002,85 +4986,109 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
+          <t>operational-times</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>close-time</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Closing time</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>hours-of-operation</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>hours-not-known</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>Hours not known</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>Applicant states they do not know the hours of operation</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>non-res-floorspace</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>non-residential-change-outline</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>non-res-floorspace</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Details of changes to non-residential floorspace in the proposed development.</t>
@@ -5088,31 +5096,23 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>floorspace-details-outline</t>
+          <t>non-residential-change-outline</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>specified-use</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5160,17 +5160,17 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>not-applicable</t>
+          <t>specified-use</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5208,12 +5208,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>not-applicable</t>
+          <t>is-existing-rooms-lost-known</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Is existing rooms lost known</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5640,7 +5640,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Used to explicitly state the use class does not apply to the proposal</t>
+          <t>Whether the total existing rooms that will be lost is known</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>is-existing-rooms-lost-known</t>
+          <t>existing-rooms-lost</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Is existing rooms lost known</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -5688,12 +5688,12 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Whether the total existing rooms that will be lost is known</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>existing-rooms-lost</t>
+          <t>is-total-rooms-proposed-known</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Is total rooms proposed known</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5736,12 +5736,12 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Whether the total rooms proposed is known</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>is-total-rooms-proposed-known</t>
+          <t>total-rooms-proposed</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Is total rooms proposed known</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5784,12 +5784,12 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Whether the total rooms proposed is known</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>total-rooms-proposed</t>
+          <t>net-additional-rooms</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Net additional rooms</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -5832,60 +5832,60 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n"/>
-      <c r="B108" s="2" t="n"/>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>room-details-outline</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>net-additional-rooms</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Net additional rooms</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -5895,16 +5895,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -5912,12 +5904,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -5928,7 +5920,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -5952,33 +5944,49 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6012,19 +6020,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -6034,7 +6042,7 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6068,19 +6076,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -6124,19 +6132,19 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -6180,19 +6188,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -6202,7 +6210,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6226,34 +6234,26 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice served date</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -6272,36 +6272,28 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>notice-date</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -6456,12 +6448,12 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
@@ -6472,17 +6464,17 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6496,12 +6488,12 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
@@ -6512,17 +6504,17 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6528,12 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
@@ -6552,36 +6544,44 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n"/>
-      <c r="B123" s="2" t="n"/>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
@@ -6592,31 +6592,23 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -6624,12 +6616,12 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -6640,17 +6632,17 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6656,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -6680,7 +6672,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -6704,12 +6696,12 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
@@ -6720,12 +6712,12 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -6744,12 +6736,12 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -6760,12 +6752,12 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -6775,21 +6767,30 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n"/>
-      <c r="B128" s="2" t="n"/>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>processes-machinery-waste</t>
+        </is>
+      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>site-activity-details</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -6800,7 +6801,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -6810,21 +6811,13 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>processes-machinery-waste</t>
-        </is>
-      </c>
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">How waste will be managed on the site
@@ -6833,12 +6826,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>site-activity-details</t>
+          <t>proposal-waste-management</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Proposal waste management</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
@@ -6849,12 +6842,12 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -6874,28 +6867,36 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>proposal-waste-management</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>waste-management-facility-type</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Waste management facility type</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -6925,12 +6926,12 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>waste-management-facility-type</t>
+          <t>total-capacity</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Waste management facility type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
@@ -6939,12 +6940,12 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -6974,12 +6975,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>total-capacity</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
@@ -6988,12 +6989,12 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -7023,12 +7024,12 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>annual-throughput</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
@@ -7037,12 +7038,12 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -7072,12 +7073,12 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>annual-throughput</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -7086,12 +7087,12 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -7111,22 +7112,22 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>municipal</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
@@ -7135,17 +7136,17 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7170,12 +7171,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>municipal</t>
+          <t>construction-demolition</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -7184,12 +7185,12 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -7219,12 +7220,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>construction-demolition</t>
+          <t>commercial-industrial</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7233,12 +7234,12 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -7268,12 +7269,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>commercial-industrial</t>
+          <t>hazardous</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
@@ -7282,12 +7283,12 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -7297,65 +7298,56 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n"/>
-      <c r="B139" s="2" t="n"/>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>hazardous</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -7363,12 +7355,12 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reserved-matters</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reserved matters[]</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -7379,12 +7371,12 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -7403,12 +7395,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>reserved-matters</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -7419,12 +7411,12 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -7443,12 +7435,12 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -7459,17 +7451,17 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7483,12 +7475,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7499,17 +7491,17 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7523,12 +7515,12 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7539,36 +7531,44 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n"/>
-      <c r="B145" s="2" t="n"/>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>res-units</t>
+        </is>
+      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>will-residential-units-change</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -7579,31 +7579,23 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>res-units</t>
-        </is>
-      </c>
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>Details of the residential units that make up both the current and proposed development.</t>
@@ -7611,28 +7603,36 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>will-residential-units-change</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>tenure-type</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>tenure-type</t>
+          <t>housing-type</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
@@ -7675,7 +7675,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -7709,26 +7709,34 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>housing-type</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>units-unknown</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -7767,19 +7775,27 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr"/>
-      <c r="K149" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -7833,27 +7849,27 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7897,27 +7913,27 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7951,37 +7967,29 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8005,39 +8013,39 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>proposed-unit-breakdown</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8071,19 +8079,27 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr"/>
-      <c r="K154" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -8137,27 +8153,27 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8201,27 +8217,27 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8255,37 +8271,29 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8299,49 +8307,33 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>total-existing-units</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>proposed-unit-breakdown</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>total-units</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8347,12 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>total-existing-units</t>
+          <t>total-proposed-units</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -8371,12 +8363,12 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -8395,12 +8387,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>total-proposed-units</t>
+          <t>net-change</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -8411,12 +8403,12 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -8426,21 +8418,29 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n"/>
-      <c r="B161" s="2" t="n"/>
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>site-area</t>
+        </is>
+      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>net-change</t>
+          <t>site-area-in-hectares</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8451,12 +8451,12 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -8466,16 +8466,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>site-area</t>
-        </is>
-      </c>
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>How big the site is including relevant measurements</t>
@@ -8483,12 +8475,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>site-area-in-hectares</t>
+          <t>site-area-provided-by</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8499,52 +8491,68 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n"/>
-      <c r="B163" s="2" t="n"/>
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>site-area-provided-by</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H163" s="2" t="inlineStr"/>
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr"/>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -8554,16 +8562,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr"/>
@@ -8595,12 +8595,12 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr"/>
@@ -8643,7 +8643,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
@@ -8677,12 +8677,12 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
@@ -8691,12 +8691,12 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
@@ -8739,12 +8739,12 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr"/>
@@ -8787,12 +8787,12 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr"/>
@@ -8835,12 +8835,12 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr"/>
@@ -8883,12 +8883,12 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -8931,7 +8931,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
@@ -8946,64 +8946,56 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n"/>
-      <c r="B172" s="2" t="n"/>
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr"/>
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
       <c r="C173" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -9011,12 +9003,12 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr"/>
@@ -9027,12 +9019,12 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -9051,12 +9043,12 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr"/>
@@ -9067,17 +9059,17 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9091,23 +9083,31 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr"/>
-      <c r="G175" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9141,12 +9141,12 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
@@ -9155,7 +9155,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -9203,7 +9203,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -9212,54 +9212,6 @@
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="n"/>
-      <c r="B178" s="2" t="n"/>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>other-contact</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M178" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -9267,50 +9219,50 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="A68:A77"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B146:B161"/>
-    <mergeCell ref="B109:B123"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="A164:A172"/>
-    <mergeCell ref="B124:B128"/>
-    <mergeCell ref="B84:B90"/>
-    <mergeCell ref="B140:B145"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B62:B67"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="A91:A108"/>
-    <mergeCell ref="A129:A139"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B41:B54"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A173:A178"/>
-    <mergeCell ref="B164:B172"/>
-    <mergeCell ref="B78:B83"/>
-    <mergeCell ref="B91:B108"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B129:B139"/>
-    <mergeCell ref="A109:A123"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A146:A161"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A124:A128"/>
-    <mergeCell ref="A84:A90"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A140:A145"/>
-    <mergeCell ref="A55"/>
-    <mergeCell ref="A41:A54"/>
-    <mergeCell ref="B68:B77"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B173:B178"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A145:A160"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A42:A55"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="A172:A177"/>
+    <mergeCell ref="A79:A84"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A163:A171"/>
+    <mergeCell ref="B92:B107"/>
+    <mergeCell ref="A85:A91"/>
+    <mergeCell ref="A108:A122"/>
+    <mergeCell ref="A92:A107"/>
+    <mergeCell ref="B123:B127"/>
+    <mergeCell ref="A69:A78"/>
+    <mergeCell ref="B128:B138"/>
+    <mergeCell ref="B63:B68"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A123:A127"/>
+    <mergeCell ref="B56"/>
+    <mergeCell ref="A139:A144"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B85:B91"/>
+    <mergeCell ref="B172:B177"/>
+    <mergeCell ref="B108:B122"/>
+    <mergeCell ref="B69:B78"/>
+    <mergeCell ref="B163:B171"/>
+    <mergeCell ref="B145:B160"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="A56"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B42:B55"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A128:A138"/>
+    <mergeCell ref="B79:B84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
+++ b/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N177"/>
+  <dimension ref="A1:N180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1980,19 +1980,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2036,19 +2044,27 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,21 +2098,37 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2130,12 +2162,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2144,12 +2176,12 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2159,56 +2191,64 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2216,31 +2256,23 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2274,29 +2306,21 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2306,7 +2330,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2340,24 +2364,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2367,64 +2391,72 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2442,29 +2474,21 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2498,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2532,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2530,7 +2554,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2564,19 +2588,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2644,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2676,77 +2700,101 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>bng-condition-applies</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2755,89 +2803,105 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>bng-condition-exemption-reasons</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>exemption-type</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2856,22 +2920,22 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>exemption-type</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2880,12 +2944,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2904,22 +2968,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2928,12 +2992,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2962,12 +3026,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2976,17 +3040,17 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3074,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -3024,17 +3088,17 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3058,39 +3122,31 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>loss-date</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Earlier date reason</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3114,39 +3170,31 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>pre-loss-biodiversity-value</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Pre loss biodiversity value</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3180,29 +3228,29 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>supporting-evidence</t>
+          <t>loss-date</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3226,26 +3274,34 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>pre-loss-biodiversity-value</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Pre loss biodiversity value</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3274,31 +3330,39 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>supporting-evidence</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3322,12 +3386,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3336,17 +3400,17 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3370,34 +3434,26 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3407,40 +3463,40 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>irreplaceable-habitats-details</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3450,50 +3506,58 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3503,21 +3567,29 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3528,7 +3600,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3538,13 +3610,21 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3552,12 +3632,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3568,34 +3648,26 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3616,7 +3688,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3626,7 +3698,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3635,17 +3707,17 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3656,23 +3728,31 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3680,12 +3760,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3696,12 +3776,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3711,53 +3791,37 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>employment</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>full-time</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration confirmed</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3771,41 +3835,33 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>part-time</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3815,8 +3871,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -3834,12 +3898,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3848,12 +3912,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3872,22 +3936,22 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3896,7 +3960,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3920,22 +3984,22 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3944,12 +4008,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3978,12 +4042,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3992,12 +4056,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -4007,39 +4071,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>existing-use</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -4048,12 +4104,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4067,27 +4123,27 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>use-details</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -4096,23 +4152,31 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>existing-use</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -4130,12 +4194,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>land-part</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -4144,12 +4208,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4168,33 +4232,41 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>use-details</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Use details</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4208,23 +4280,31 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>land-part</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4234,7 +4314,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4328,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4264,17 +4344,17 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4368,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4304,17 +4384,17 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4408,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4344,17 +4424,17 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4448,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4384,7 +4464,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -4408,12 +4488,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4424,44 +4504,36 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-area</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4472,7 +4544,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4491,17 +4563,17 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>data-provided-by</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4512,12 +4584,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4527,8 +4599,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Results of any flood risk assessments made for the development site</t>
@@ -4536,12 +4616,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4552,17 +4632,17 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4656,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4592,17 +4672,17 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4696,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4632,17 +4712,17 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4736,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4672,12 +4752,12 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -4687,53 +4767,37 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>hrs-operation</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Increases flood risk</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -4747,52 +4811,52 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>use-other</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Use other</t>
-        </is>
-      </c>
+          <t>Surface water disposal[]</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -4810,29 +4874,21 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>schedule-days</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -4866,34 +4922,26 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4932,32 +4980,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>open-time</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Schedule days[]</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4996,37 +5036,29 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>close-time</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5050,74 +5082,106 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>hours-not-known</t>
+          <t>operational-times</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>open-time</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>non-res-floorspace</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>non-residential-change-outline</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>operational-times</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>close-time</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -5131,27 +5195,27 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>floorspace-details-outline</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>hours-not-known</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Hours not known</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5160,23 +5224,31 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>non-res-floorspace</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Details of changes to non-residential floorspace in the proposed development.</t>
@@ -5184,41 +5256,33 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>floorspace-details-outline</t>
+          <t>non-residential-change-outline</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>specified-use</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5242,12 +5306,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>existing-gross-floorspace</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5256,12 +5320,12 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -5290,12 +5354,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>is-floorspace-lost-known</t>
+          <t>specified-use</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Is floorspace lost known</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5304,12 +5368,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Whether the amount of floorspace to be lost is known</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -5338,12 +5402,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>floorspace-lost</t>
+          <t>existing-gross-floorspace</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -5352,7 +5416,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -5362,7 +5426,7 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5450,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>is-total-gross-proposed-known</t>
+          <t>is-floorspace-lost-known</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Is total gross proposed known</t>
+          <t>Is floorspace lost known</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5400,7 +5464,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Whether the total gross proposed floorspace is known</t>
+          <t>Whether the amount of floorspace to be lost is known</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -5434,12 +5498,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>total-gross-proposed</t>
+          <t>floorspace-lost</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5448,7 +5512,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -5482,12 +5546,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>net-additional-floorspace</t>
+          <t>is-total-gross-proposed-known</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Is total gross proposed known</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5496,17 +5560,17 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Whether the total gross proposed floorspace is known</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5520,22 +5584,22 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>room-details-outline</t>
+          <t>floorspace-details-outline</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>use-class-accommodation</t>
+          <t>total-gross-proposed</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5544,17 +5608,17 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5568,22 +5632,22 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>room-details-outline</t>
+          <t>floorspace-details-outline</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>net-additional-floorspace</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5592,17 +5656,17 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5690,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>is-existing-rooms-lost-known</t>
+          <t>use-class-accommodation</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Is existing rooms lost known</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5640,17 +5704,17 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Whether the total existing rooms that will be lost is known</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5738,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>existing-rooms-lost</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -5688,12 +5752,12 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -5722,12 +5786,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>is-total-rooms-proposed-known</t>
+          <t>is-existing-rooms-lost-known</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Is total rooms proposed known</t>
+          <t>Is existing rooms lost known</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5736,7 +5800,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Whether the total rooms proposed is known</t>
+          <t>Whether the total existing rooms that will be lost is known</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -5770,12 +5834,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>total-rooms-proposed</t>
+          <t>existing-rooms-lost</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5784,7 +5848,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -5818,12 +5882,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>net-additional-rooms</t>
+          <t>is-total-rooms-proposed-known</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms</t>
+          <t>Is total rooms proposed known</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -5832,65 +5896,65 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Whether the total rooms proposed is known</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>room-details-outline</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>total-rooms-proposed</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Total rooms proposed</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5899,33 +5963,41 @@
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>room-details-outline</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>net-additional-rooms</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Net additional rooms</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -5935,8 +6007,16 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n"/>
-      <c r="B110" s="2" t="n"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -5944,49 +6024,33 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6000,44 +6064,28 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -6076,19 +6124,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -6098,7 +6146,7 @@
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6132,19 +6180,19 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -6188,19 +6236,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -6210,7 +6258,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6234,31 +6282,47 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>notice-served-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6272,28 +6336,52 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -6312,23 +6400,47 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -6352,22 +6464,22 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -6376,17 +6488,17 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6400,41 +6512,33 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6448,12 +6552,12 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
@@ -6464,7 +6568,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -6474,7 +6578,7 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6488,28 +6592,36 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -6528,23 +6640,31 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -6559,29 +6679,21 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
@@ -6592,12 +6704,12 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -6611,17 +6723,17 @@
       <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -6632,17 +6744,17 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6651,17 +6763,17 @@
       <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -6672,23 +6784,31 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n"/>
-      <c r="B126" s="2" t="n"/>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -6696,12 +6816,12 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
@@ -6712,17 +6832,17 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6736,12 +6856,12 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -6752,7 +6872,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -6767,30 +6887,21 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>processes-machinery-waste</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>site-activity-details</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -6801,7 +6912,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -6811,7 +6922,7 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6820,18 +6931,17 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>proposal-waste-management</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
@@ -6842,17 +6952,17 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6861,53 +6971,52 @@
       <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>waste-management-facility-type</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>Waste management facility type</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n"/>
-      <c r="B131" s="2" t="n"/>
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>processes-machinery-waste</t>
+        </is>
+      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">How waste will be managed on the site
@@ -6916,36 +7025,28 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>site-activity-details</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>total-capacity</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Total capacity</t>
-        </is>
-      </c>
+          <t>Site activity details</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -6965,36 +7066,28 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>proposal-waste-management</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>unit-type</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Unit type</t>
-        </is>
-      </c>
+          <t>Proposal waste management</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -7024,12 +7117,12 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>annual-throughput</t>
+          <t>waste-management-facility-type</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Waste management facility type</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
@@ -7038,12 +7131,12 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -7073,12 +7166,12 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>total-capacity</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -7087,12 +7180,12 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -7112,22 +7205,22 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>municipal</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
@@ -7136,17 +7229,17 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7161,22 +7254,22 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>construction-demolition</t>
+          <t>annual-throughput</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -7185,7 +7278,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -7195,7 +7288,7 @@
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7210,22 +7303,22 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>commercial-industrial</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7234,17 +7327,17 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7269,12 +7362,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>hazardous</t>
+          <t>municipal</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Hazardous</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
@@ -7283,7 +7376,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -7298,50 +7391,51 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>construction-demolition</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Construction demolition</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7350,38 +7444,47 @@
       <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>reserved-matters</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>commercial-industrial</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Commercial industrial</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7390,44 +7493,61 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>hazardous</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -7435,12 +7555,12 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -7451,17 +7571,17 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7475,12 +7595,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>reserved-matters</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Reserved matters[]</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7491,12 +7611,12 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -7515,12 +7635,12 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7531,44 +7651,36 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>res-units</t>
-        </is>
-      </c>
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>will-residential-units-change</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -7579,17 +7691,17 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7598,41 +7710,33 @@
       <c r="B146" s="2" t="n"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>tenure-type</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>Tenure type</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -7646,52 +7750,52 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>housing-type</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Housing type</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="n"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>res-units</t>
+        </is>
+      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Details of the residential units that make up both the current and proposed development.</t>
@@ -7699,39 +7803,23 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>will-residential-units-change</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>existing-unit-breakdown</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>units-unknown</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
+          <t>Residential unit change</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -7765,42 +7853,26 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>tenure-type</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>units-per-bedroom-no</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>no-bedrooms-unknown</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>No bedrooms unknown</t>
-        </is>
-      </c>
+          <t>Tenure type</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -7829,47 +7901,31 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>housing-type</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>units-per-bedroom-no</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>no-of-bedrooms</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Housing type</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7903,32 +7959,24 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -7967,29 +8015,37 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr"/>
-      <c r="K152" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8013,39 +8069,47 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>proposed-unit-breakdown</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr"/>
-      <c r="K153" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>no-of-bedrooms</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8133,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>proposed-unit-breakdown</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8089,22 +8153,22 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -8133,37 +8197,29 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>proposed-unit-breakdown</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>no-of-bedrooms</t>
-        </is>
-      </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
@@ -8207,32 +8263,24 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -8271,29 +8319,37 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="inlineStr"/>
-      <c r="K157" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8307,23 +8363,47 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>total-existing-units</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>proposed-unit-breakdown</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>units-per-bedroom-no</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>no-of-bedrooms</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -8333,7 +8413,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8347,23 +8427,47 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>total-proposed-units</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>proposed-unit-breakdown</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>units-per-bedroom-no</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
@@ -8387,23 +8491,39 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>net-change</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>proposed-unit-breakdown</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>total-units</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -8413,34 +8533,26 @@
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>site-area</t>
-        </is>
-      </c>
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>site-area-in-hectares</t>
+          <t>total-existing-units</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Total existing units</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8451,12 +8563,12 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -8470,17 +8582,17 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>site-area-provided-by</t>
+          <t>total-proposed-units</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8491,121 +8603,105 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>net-change</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Net change</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr"/>
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr"/>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="2" t="n"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>site-area</t>
+        </is>
+      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>site-area-in-hectares</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Site area in hectares</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr"/>
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8614,41 +8710,33 @@
       <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>site-area-provided-by</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Site area provided by</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr"/>
       <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="2" t="inlineStr"/>
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -8658,8 +8746,16 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="2" t="n"/>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -8677,12 +8773,12 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
@@ -8691,17 +8787,17 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8725,31 +8821,39 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J167" s="2" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8773,26 +8877,34 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr"/>
-      <c r="I168" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -8821,26 +8933,34 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J169" s="2" t="inlineStr"/>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -8869,21 +8989,29 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr"/>
-      <c r="I170" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
@@ -8917,12 +9045,12 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -8931,12 +9059,12 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -8946,50 +9074,50 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>northing</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="H172" s="2" t="inlineStr"/>
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8998,38 +9126,46 @@
       <c r="B173" s="2" t="n"/>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr"/>
-      <c r="G173" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H173" s="2" t="inlineStr"/>
       <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="2" t="inlineStr"/>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9038,33 +9174,41 @@
       <c r="B174" s="2" t="n"/>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr"/>
-      <c r="G174" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H174" s="2" t="inlineStr"/>
       <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -9074,8 +9218,16 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n"/>
-      <c r="B175" s="2" t="n"/>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -9083,36 +9235,28 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
@@ -9131,36 +9275,28 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr"/>
       <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
@@ -9179,39 +9315,175 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="2" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M177" s="2" t="inlineStr">
+      <c r="M180" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N177" s="2" t="inlineStr">
+      <c r="N180" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -9219,50 +9491,50 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A145:A160"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A42:A55"/>
+    <mergeCell ref="A87:A93"/>
+    <mergeCell ref="B44:B57"/>
+    <mergeCell ref="A126:A130"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="B81:B86"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A172:A177"/>
-    <mergeCell ref="A79:A84"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A163:A171"/>
-    <mergeCell ref="B92:B107"/>
-    <mergeCell ref="A85:A91"/>
-    <mergeCell ref="A108:A122"/>
-    <mergeCell ref="A92:A107"/>
-    <mergeCell ref="B123:B127"/>
-    <mergeCell ref="A69:A78"/>
-    <mergeCell ref="B128:B138"/>
-    <mergeCell ref="B63:B68"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A123:A127"/>
-    <mergeCell ref="B56"/>
-    <mergeCell ref="A139:A144"/>
-    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A44:A57"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A58"/>
+    <mergeCell ref="B87:B93"/>
+    <mergeCell ref="B166:B174"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="B126:B130"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B110:B125"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="A65:A70"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="A131:A141"/>
+    <mergeCell ref="B175:B180"/>
+    <mergeCell ref="B58"/>
+    <mergeCell ref="B94:B109"/>
+    <mergeCell ref="A110:A125"/>
+    <mergeCell ref="A148:A163"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B85:B91"/>
-    <mergeCell ref="B172:B177"/>
-    <mergeCell ref="B108:B122"/>
-    <mergeCell ref="B69:B78"/>
-    <mergeCell ref="B163:B171"/>
-    <mergeCell ref="B145:B160"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A175:A180"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A94:A109"/>
+    <mergeCell ref="A71:A80"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B65:B70"/>
+    <mergeCell ref="A166:A174"/>
+    <mergeCell ref="B131:B141"/>
+    <mergeCell ref="A24:A32"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="B148:B163"/>
+    <mergeCell ref="A81:A86"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A128:A138"/>
-    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="A142:A147"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
